--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["hero-video","cards-stats","columns-feature","columns-feature","columns-feature","cards-logos","columns-stock","carousel-news"]</t>
+    <t>["hero-image","cards-stats","columns-feature","columns-feature","columns-feature","cards-logos","columns-stock","carousel-news"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-12T23:20:05.202Z</t>
+    <t>2026-08-13T15:32:22.024Z</t>
   </si>
   <si>
     <t>Home | Covista</t>
